--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536136_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536136_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,31 +558,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1814</v>
+        <v>9.703900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2617</v>
+        <v>8.7843</v>
       </c>
       <c r="F2" t="n">
         <v>0.9196</v>
       </c>
       <c r="G2" t="n">
-        <v>4.686</v>
+        <v>6.2086</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2773</v>
+        <v>1.5848</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4087</v>
+        <v>4.6238</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6343</v>
+        <v>7.1569</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3782</v>
+        <v>2.6857</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2561</v>
+        <v>4.4712</v>
       </c>
       <c r="M2" t="n">
         <v>-0.9483</v>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>J. PLEASANT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,64 +890,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5226</v>
+        <v>-0.5193</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5226</v>
+        <v>-0.8007</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.2814</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5226</v>
+        <v>-1.7633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3075</v>
+        <v>-4.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>1.215</v>
+        <v>2.3119</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5226</v>
+        <v>-0.3444</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3075</v>
+        <v>-3.0415</v>
       </c>
       <c r="L6" t="n">
-        <v>1.215</v>
+        <v>2.6971</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.0337</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.3852</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.195</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.7549</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.0596</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0051</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.0545</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PLEASANT</t>
+          <t>R. ISSANZA TSHUKA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5193</v>
+        <v>-0.8555</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8007</v>
+        <v>-0.8762</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2814</v>
+        <v>0.0207</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7633</v>
+        <v>0.2278</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.0752</v>
+        <v>0.0672</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3119</v>
+        <v>0.1606</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3444</v>
+        <v>0.5626</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.0415</v>
+        <v>0.2791</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6971</v>
+        <v>0.2835</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4189</v>
+        <v>-0.3348</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0337</v>
+        <v>-0.2119</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3852</v>
+        <v>-0.1229</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.195</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7549</v>
+        <v>0.7799</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0596</v>
+        <v>1.1156</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0051</v>
+        <v>1.174</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0545</v>
+        <v>-0.0584</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4986</v>
+        <v>-1.029</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4986</v>
+        <v>-0.6629</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.366</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. ISSANZA TSHUKA</t>
+          <t>S. CHABI YO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8555</v>
+        <v>-1.0082</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8762</v>
+        <v>-0.3893</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0207</v>
+        <v>-0.6189</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2278</v>
+        <v>-0.4448</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0672</v>
+        <v>-0.5649</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1606</v>
+        <v>0.1201</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5626</v>
+        <v>0.9116</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2791</v>
+        <v>0.6686</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2835</v>
+        <v>0.243</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3348</v>
+        <v>-1.3565</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2119</v>
+        <v>-1.2335</v>
       </c>
       <c r="O8" t="n">
         <v>-0.1229</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1699</v>
+        <v>0.9749</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7799</v>
+        <v>1.9499</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1156</v>
+        <v>-0.5968</v>
       </c>
       <c r="T8" t="n">
-        <v>1.174</v>
+        <v>-0.6045</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0584</v>
+        <v>0.0077</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.029</v>
+        <v>-0.9415</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6629</v>
+        <v>0.2786</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.366</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CHABI YO</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0082</v>
+        <v>-2.0286</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3893</v>
+        <v>-1.0837</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6189</v>
+        <v>-0.9449</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4448</v>
+        <v>-1.5116</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5649</v>
+        <v>-0.3856</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1201</v>
+        <v>-1.126</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9116</v>
+        <v>-0.2225</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6686</v>
+        <v>0.369</v>
       </c>
       <c r="L9" t="n">
-        <v>0.243</v>
+        <v>-0.5915</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3565</v>
+        <v>-1.2891</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2335</v>
+        <v>-0.7546</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1229</v>
+        <v>-0.5345</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9749</v>
+        <v>-0.195</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9499</v>
+        <v>0.7799</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5968</v>
+        <v>-0.2346</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6045</v>
+        <v>-0.1648</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0077</v>
+        <v>-0.0697</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9415</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>0.2786</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2201</v>
+        <v>-0.366</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,64 +1222,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0286</v>
+        <v>-2.8352</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0837</v>
+        <v>-3.0284</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9449</v>
+        <v>0.1932</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5116</v>
+        <v>-2.0673</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3856</v>
+        <v>-1.4937</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.126</v>
+        <v>-0.5736</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2225</v>
+        <v>-1.7949</v>
       </c>
       <c r="K10" t="n">
-        <v>0.369</v>
+        <v>-1.0819</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5915</v>
+        <v>-0.713</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2891</v>
+        <v>-0.2724</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7546</v>
+        <v>-0.4118</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5345</v>
+        <v>0.1394</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.195</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7799</v>
+        <v>0.9749</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2346</v>
+        <v>0.2611</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1648</v>
+        <v>0.4044</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0697</v>
+        <v>-0.1433</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-1.029</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2786</v>
+        <v>-0.6629</v>
       </c>
       <c r="X10" t="n">
         <v>-0.366</v>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8352</v>
+        <v>-3.5824</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0284</v>
+        <v>-1.0305</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1932</v>
+        <v>-2.5519</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0673</v>
+        <v>-0.7912</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4937</v>
+        <v>-0.2421</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5736</v>
+        <v>-0.5491</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7949</v>
+        <v>0.8391</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0819</v>
+        <v>0.7176</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.713</v>
+        <v>0.1215</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2724</v>
+        <v>-1.6302</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4118</v>
+        <v>-0.9596</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1394</v>
+        <v>-0.6706</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9749</v>
+        <v>-2.9248</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9749</v>
+        <v>1.3649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2611</v>
+        <v>-0.3082</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4044</v>
+        <v>-0.1648</v>
       </c>
       <c r="U11" t="n">
         <v>-0.1433</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.029</v>
+        <v>-0.9231</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6629</v>
+        <v>1.2201</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.366</v>
+        <v>-2.1432</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,157 +1388,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5824</v>
+        <v>9.685900000000004</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0305</v>
+        <v>13.48</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5519</v>
+        <v>-3.794</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7912</v>
+        <v>10.4442</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2421</v>
+        <v>-5.806</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5491</v>
+        <v>16.2502</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8391</v>
+        <v>18.9005</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7176</v>
+        <v>1.4213</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1215</v>
+        <v>17.4792</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6302</v>
+        <v>-8.4565</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9596</v>
+        <v>-7.227200000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6706</v>
+        <v>-1.229</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5599</v>
+        <v>-1.9499</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9248</v>
+        <v>-15.5988</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3649</v>
+        <v>13.6489</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3082</v>
+        <v>-0.8640000000000003</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1648</v>
+        <v>0.1254999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1433</v>
+        <v>-0.9892000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9231</v>
+        <v>2.0556</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2201</v>
+        <v>10.0533</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1432</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>play_by_play_2536136_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-7.9973</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. STARLABS MORÓN</t>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.686000000000003</v>
+        <v>2.4296</v>
       </c>
       <c r="E13" t="n">
-        <v>13.48</v>
+        <v>3.9411</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.794</v>
+        <v>-1.5116</v>
       </c>
       <c r="G13" t="n">
-        <v>10.4442</v>
+        <v>2.4589</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.806</v>
+        <v>1.4351</v>
       </c>
       <c r="I13" t="n">
-        <v>16.2501</v>
+        <v>1.0238</v>
       </c>
       <c r="J13" t="n">
-        <v>18.9005</v>
+        <v>4.8893</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4213</v>
+        <v>1.7142</v>
       </c>
       <c r="L13" t="n">
-        <v>17.4791</v>
+        <v>3.1751</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.4565</v>
+        <v>-2.4304</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.227200000000001</v>
+        <v>-0.2791</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.229</v>
+        <v>-2.1513</v>
       </c>
       <c r="P13" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-1.9499</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-15.5988</v>
-      </c>
       <c r="R13" t="n">
-        <v>13.6489</v>
+        <v>2.5348</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8640000000000001</v>
+        <v>0.1868</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1254999999999998</v>
+        <v>-0.2184</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9892</v>
+        <v>0.4052</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0556</v>
+        <v>-0.8011</v>
       </c>
       <c r="W13" t="n">
-        <v>10.0533</v>
+        <v>1.2201</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.997299999999999</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+        <v>-2.0212</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2536136_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,67 +1550,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4296</v>
+        <v>1.7459</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9411</v>
+        <v>5.5102</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5116</v>
+        <v>-3.7643</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4589</v>
+        <v>2.4266</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4351</v>
+        <v>2.7506</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0238</v>
+        <v>-0.324</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8893</v>
+        <v>5.6605</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7142</v>
+        <v>2.4853</v>
       </c>
       <c r="L14" t="n">
         <v>3.1751</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4304</v>
+        <v>-3.2338</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2791</v>
+        <v>0.2653</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1513</v>
+        <v>-3.4991</v>
       </c>
       <c r="P14" t="n">
-        <v>0.585</v>
+        <v>0.195</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5348</v>
+        <v>2.1448</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1868</v>
+        <v>0.3099</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2184</v>
+        <v>0.0224</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4052</v>
+        <v>0.2874</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8011</v>
+        <v>-1.1855</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2201</v>
+        <v>1.7772</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.0212</v>
+        <v>-2.9627</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7459</v>
+        <v>0.4637</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5102</v>
+        <v>2.6671</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.7643</v>
+        <v>-2.2034</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4266</v>
+        <v>1.1374</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7506</v>
+        <v>3.2449</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.324</v>
+        <v>-2.1075</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6605</v>
+        <v>3.4218</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4853</v>
+        <v>2.5713</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1751</v>
+        <v>0.8505</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.2338</v>
+        <v>-2.2844</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2653</v>
+        <v>0.6736</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.4991</v>
+        <v>-2.958</v>
       </c>
       <c r="P15" t="n">
-        <v>0.195</v>
+        <v>-0.39</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1448</v>
+        <v>1.5599</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3099</v>
+        <v>0.5012</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0224</v>
+        <v>0.4124</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2874</v>
+        <v>0.0888</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1855</v>
+        <v>-0.785</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7772</v>
+        <v>0.7827</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.9627</v>
+        <v>-1.5677</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.215</v>
+        <v>-0.0236</v>
       </c>
       <c r="E16" t="n">
-        <v>1.215</v>
+        <v>2.9319</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-2.9555</v>
       </c>
       <c r="G16" t="n">
-        <v>1.215</v>
+        <v>-3.0294</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.4288</v>
       </c>
       <c r="I16" t="n">
-        <v>1.215</v>
+        <v>-2.6006</v>
       </c>
       <c r="J16" t="n">
-        <v>1.215</v>
+        <v>-0.7974</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.0536</v>
       </c>
       <c r="L16" t="n">
-        <v>1.215</v>
+        <v>-0.851</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-2.232</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.4824</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.7496</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.7549</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.7549</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.4006</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.3277</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5226</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.3287</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.8061</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4637</v>
+        <v>-0.0892</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6671</v>
+        <v>-0.1753</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2034</v>
+        <v>0.0861</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1374</v>
+        <v>-0.7502</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2449</v>
+        <v>-0.2124</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1075</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4218</v>
+        <v>0.6765</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5713</v>
+        <v>0.6765</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8505</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2844</v>
+        <v>-1.4268</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6736</v>
+        <v>-0.889</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.958</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.39</v>
+        <v>-0.195</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5599</v>
+        <v>0.7799</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5012</v>
+        <v>0.1931</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4124</v>
+        <v>0.1231</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0888</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.785</v>
+        <v>0.6629</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7827</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5677</v>
+        <v>0.6629</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>L. GARCIA MUNOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0236</v>
+        <v>-1.2325</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9319</v>
+        <v>-2.1434</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.9555</v>
+        <v>0.911</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0294</v>
+        <v>-3.0279</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4288</v>
+        <v>-0.9784</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6006</v>
+        <v>-2.0496</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7974</v>
+        <v>-1.8815</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0536</v>
+        <v>-1.1765</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.851</v>
+        <v>-0.705</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.232</v>
+        <v>-1.1464</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4824</v>
+        <v>0.1981</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7496</v>
+        <v>-1.3446</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7549</v>
+        <v>0.7799</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R18" t="n">
         <v>1.7549</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.3181</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4006</v>
+        <v>0.1559</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3277</v>
+        <v>0.1622</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5226</v>
+        <v>0.6975</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3287</v>
+        <v>0.5571</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.8061</v>
+        <v>0.1404</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0892</v>
+        <v>-2.062</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1753</v>
+        <v>-0.2881</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0861</v>
+        <v>-1.7738</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7502</v>
+        <v>-2.6929</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2124</v>
+        <v>-0.4248</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-2.2681</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6765</v>
+        <v>-0.3955</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6765</v>
+        <v>0.123</v>
       </c>
       <c r="L19" t="n">
+        <v>-0.5185</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-2.2974</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.5479000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.7496</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.7799</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-1.4268</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.889</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.5377999999999999</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.195</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-0.9749</v>
       </c>
       <c r="R19" t="n">
         <v>0.7799</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1931</v>
+        <v>0.1296</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1231</v>
+        <v>0.1074</v>
       </c>
       <c r="U19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6629</v>
+        <v>-0.2786</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6629</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.062</v>
+        <v>-2.9817</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2881</v>
+        <v>-3.8291</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7738</v>
+        <v>0.8474</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6929</v>
+        <v>-2.5229</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4248</v>
+        <v>0.332</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2681</v>
+        <v>-2.8549</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3955</v>
+        <v>-2.0455</v>
       </c>
       <c r="K20" t="n">
-        <v>0.123</v>
+        <v>0.6765</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5185</v>
+        <v>-2.7221</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2974</v>
+        <v>-0.4774</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.3446</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7496</v>
+        <v>-0.1328</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7799</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R20" t="n">
         <v>0.7799</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1296</v>
+        <v>0.1701</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1074</v>
+        <v>0.1663</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0222</v>
+        <v>0.0039</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2786</v>
+        <v>0.5409</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2786</v>
+        <v>0.5409</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. GARCIA MUNOZ</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4475</v>
+        <v>-3.0075</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3585</v>
+        <v>-3.0568</v>
       </c>
       <c r="F21" t="n">
-        <v>0.911</v>
+        <v>0.0494</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.243</v>
+        <v>-2.5711</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9784</v>
+        <v>-0.7306</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.2646</v>
+        <v>-1.8405</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.0966</v>
+        <v>-0.9475</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1765</v>
+        <v>-0.3155</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.92</v>
+        <v>-0.632</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1464</v>
+        <v>-1.6236</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1981</v>
+        <v>-0.4152</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3446</v>
+        <v>-1.2085</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7799</v>
+        <v>-0.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7549</v>
+        <v>1.5599</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3181</v>
+        <v>0.1976</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1559</v>
+        <v>-0.1595</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1622</v>
+        <v>0.3572</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6975</v>
+        <v>-0.244</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5571</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1404</v>
+        <v>-0.244</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>D. ABREU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9817</v>
+        <v>-3.2734</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8291</v>
+        <v>-1.8164</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8474</v>
+        <v>-1.457</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5229</v>
+        <v>-1.8727</v>
       </c>
       <c r="H22" t="n">
-        <v>0.332</v>
+        <v>0.8183</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8549</v>
+        <v>-2.691</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0455</v>
+        <v>-0.1244</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6765</v>
+        <v>0.4186</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.7221</v>
+        <v>-0.543</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4774</v>
+        <v>-1.7483</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3446</v>
+        <v>0.3997</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1328</v>
+        <v>-2.148</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1699</v>
+        <v>-0</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7799</v>
+        <v>1.9499</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1701</v>
+        <v>-0.2153</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1663</v>
+        <v>-0.0208</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0039</v>
+        <v>-0.1945</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5409</v>
+        <v>-1.1855</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5409</v>
+        <v>-1.4641</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,235 +2297,69 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0075</v>
+        <v>-8.0307</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0568</v>
+        <v>3.7412</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0494</v>
+        <v>-11.7717</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5711</v>
+        <v>-10.4442</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7306</v>
+        <v>5.805899999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8405</v>
+        <v>-16.2502</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9475</v>
+        <v>8.456300000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3155</v>
+        <v>7.227</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.632</v>
+        <v>1.2291</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6236</v>
+        <v>-18.9005</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4152</v>
+        <v>-1.4215</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2085</v>
+        <v>-17.4793</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.39</v>
+        <v>1.9498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9499</v>
+        <v>-13.6492</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5599</v>
+        <v>15.5988</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1976</v>
+        <v>2.5194</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1595</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3572</v>
+        <v>1.5301</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.244</v>
+        <v>-2.0558</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>7.9444</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.244</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>play_by_play_2536136_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>D. ABREU</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-3.2734</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-1.8164</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-1.457</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-1.8727</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.8183</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-2.691</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-0.1244</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.4186</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-0.543</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-1.7483</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.3997</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-2.148</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-1.9499</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.9499</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-0.2153</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-0.0208</v>
-      </c>
-      <c r="U24" t="n">
-        <v>-0.1945</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-1.1855</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.2786</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-1.4641</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536136_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-8.0307</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3.7411</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-11.7717</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-10.4443</v>
-      </c>
-      <c r="H25" t="n">
-        <v>5.8059</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-16.2502</v>
-      </c>
-      <c r="J25" t="n">
-        <v>8.456200000000003</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7.226999999999999</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.2291</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-18.9005</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-1.4215</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-17.4793</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.9498</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-13.6492</v>
-      </c>
-      <c r="R25" t="n">
-        <v>15.5988</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5194</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.9894000000000002</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.5301</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-2.0558</v>
-      </c>
-      <c r="W25" t="n">
-        <v>7.944400000000001</v>
-      </c>
-      <c r="X25" t="n">
         <v>-10.0002</v>
       </c>
-      <c r="Y25" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
